--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_desktop_navigation.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/persona/primary_persona_vs_desktop_navigation.xlsx
@@ -465,13 +465,13 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -484,13 +484,13 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -509,7 +509,7 @@
         <v>5</v>
       </c>
       <c r="E4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5">
@@ -522,7 +522,7 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
         <v>6</v>
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -560,10 +560,10 @@
         <v>17</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>15</v>
